--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33524-2025 artfynd.xlsx
+++ b/artfynd/A 33524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131732773</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739564</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
